--- a/manual-testing/test-cases.xlsx
+++ b/manual-testing/test-cases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajsh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code Playground\qa project\ecommerce-qa-automation\manual-testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF44841E-8961-4B6E-A534-5874D5A6FE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B5C65D-84D1-4635-9107-C6D685560560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -20,13 +20,14 @@
     <sheet name="Cart" sheetId="5" r:id="rId5"/>
     <sheet name="Checkout" sheetId="6" r:id="rId6"/>
     <sheet name="My Account" sheetId="7" r:id="rId7"/>
+    <sheet name="Bugs" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="274">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -901,12 +902,90 @@
 2. Open cart 
 3. Click Checkout</t>
   </si>
+  <si>
+    <t>TC-057</t>
+  </si>
+  <si>
+    <t>Verify password field stays masked on mobile</t>
+  </si>
+  <si>
+    <t>1. Open login page on mobile 
+2. Tap password field
+3. Enter password 
+4. Observe field</t>
+  </si>
+  <si>
+    <t>Password remains masked at all times</t>
+  </si>
+  <si>
+    <t>Password briefly visible before masking</t>
+  </si>
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>Bug Summary</t>
+  </si>
+  <si>
+    <t>BUG-001</t>
+  </si>
+  <si>
+    <t>BUG-002</t>
+  </si>
+  <si>
+    <t>BUG-003</t>
+  </si>
+  <si>
+    <t>BUG-004</t>
+  </si>
+  <si>
+    <t>BUG-005</t>
+  </si>
+  <si>
+    <t>BUG-006</t>
+  </si>
+  <si>
+    <t>BUG-007</t>
+  </si>
+  <si>
+    <t>BUG-008</t>
+  </si>
+  <si>
+    <t>Cart total not updating without clicking Update</t>
+  </si>
+  <si>
+    <t>Guest checkout allows empty billing name</t>
+  </si>
+  <si>
+    <t>Password field briefly unmasks on mobile</t>
+  </si>
+  <si>
+    <t>Special characters in search cause blank page</t>
+  </si>
+  <si>
+    <t>Product image broken on slow connection</t>
+  </si>
+  <si>
+    <t>Cart quantity accepts 0 without error</t>
+  </si>
+  <si>
+    <t>Back button during checkout loses cart data</t>
+  </si>
+  <si>
+    <t>TC-033, TC-043</t>
+  </si>
+  <si>
+    <t>Product Page, Cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linked Test Case(s) </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -915,6 +994,16 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -1060,7 +1149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1100,6 +1189,49 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1607,12 +1739,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="32" style="4" customWidth="1"/>
     <col min="4" max="4" width="55" style="4" customWidth="1"/>
     <col min="5" max="5" width="42" style="4" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1936,6 +2068,35 @@
       </c>
       <c r="I11" s="13" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="55.2">
+      <c r="A12" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -3225,4 +3386,180 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49DA1B9F-BD94-4BDE-82E4-461C86B23AB2}">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="38.796875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.8984375" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.09765625" style="27" customWidth="1"/>
+    <col min="6" max="6" width="11.8984375" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="11" max="11" width="8.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="19.2" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="25"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="24"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="26"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="10"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="28"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="13"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="D8" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="5"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/manual-testing/test-cases.xlsx
+++ b/manual-testing/test-cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code Playground\qa project\ecommerce-qa-automation\manual-testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B5C65D-84D1-4635-9107-C6D685560560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933C48D9-5E85-43E3-B346-F86C917F60C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="289">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -95,27 +95,18 @@
     <t>Register with empty first name</t>
   </si>
   <si>
-    <t>Validation error on first name field</t>
-  </si>
-  <si>
     <t>TC-004</t>
   </si>
   <si>
     <t>Register with invalid email format</t>
   </si>
   <si>
-    <t>Email format validation error shown</t>
-  </si>
-  <si>
     <t>TC-005</t>
   </si>
   <si>
     <t>Register with mismatched passwords</t>
   </si>
   <si>
-    <t>Error: "Passwords do not match"</t>
-  </si>
-  <si>
     <t>TC-006</t>
   </si>
   <si>
@@ -158,9 +149,6 @@
     <t>Register with very long first name</t>
   </si>
   <si>
-    <t>Either accepts or shows max length error</t>
-  </si>
-  <si>
     <t>TC-010</t>
   </si>
   <si>
@@ -188,27 +176,18 @@
     <t>Login with wrong password</t>
   </si>
   <si>
-    <t>Error: "Login was unsuccessful. Please correct the errors and try again"</t>
-  </si>
-  <si>
     <t>TC-013</t>
   </si>
   <si>
     <t>Login with unregistered email</t>
   </si>
   <si>
-    <t>Error message shown for invalid credentials</t>
-  </si>
-  <si>
     <t>TC-014</t>
   </si>
   <si>
     <t>Login with empty email field</t>
   </si>
   <si>
-    <t>Validation error on email field</t>
-  </si>
-  <si>
     <t>TC-015</t>
   </si>
   <si>
@@ -224,9 +203,6 @@
     <t>Login with both fields empty</t>
   </si>
   <si>
-    <t>Validation errors on both fields</t>
-  </si>
-  <si>
     <t>TC-017</t>
   </si>
   <si>
@@ -306,9 +282,6 @@
   </si>
   <si>
     <t>Search with special characters</t>
-  </si>
-  <si>
-    <t>No results shown or validation error, no page crash</t>
   </si>
   <si>
     <t>Fail</t>
@@ -688,11 +661,6 @@
   <si>
     <t>1. Go to /register 
 2. Enter different values in Password and Confirm Password 
-3. Click Register</t>
-  </si>
-  <si>
-    <t>1. Go to /register 
-2. Enter "123" as password 
 3. Click Register</t>
   </si>
   <si>
@@ -979,6 +947,89 @@
   </si>
   <si>
     <t xml:space="preserve">Linked Test Case(s) </t>
+  </si>
+  <si>
+    <t>Validation error on first name field 
+Error message: "First name is required."</t>
+  </si>
+  <si>
+    <t>Email format validation error shown 
+Error message: "Please enter a valid email address."</t>
+  </si>
+  <si>
+    <t>Error: "The password and confirmation password do not match."</t>
+  </si>
+  <si>
+    <t>Accepts</t>
+  </si>
+  <si>
+    <t>Error: "Login was unsuccessful. Please correct the errors and try again. The credentials provided are incorrect"</t>
+  </si>
+  <si>
+    <t>Error message shown for invalid credentials
+Error: "Login was unsuccessful. Please correct the errors and try again. No customer account found"</t>
+  </si>
+  <si>
+    <t>Validation error on email field
+Error: "Please enter your email"</t>
+  </si>
+  <si>
+    <t>Validation errors</t>
+  </si>
+  <si>
+    <t>BUG-009</t>
+  </si>
+  <si>
+    <t>BUG-010</t>
+  </si>
+  <si>
+    <t>BUG-011</t>
+  </si>
+  <si>
+    <t>BUG-012</t>
+  </si>
+  <si>
+    <t>BUG-013</t>
+  </si>
+  <si>
+    <t>Single character name accepted</t>
+  </si>
+  <si>
+    <t>Weak password accepted</t>
+  </si>
+  <si>
+    <t>Password under 8 chars accepted</t>
+  </si>
+  <si>
+    <t>TC-058</t>
+  </si>
+  <si>
+    <t>No confirmation email</t>
+  </si>
+  <si>
+    <t>Phone number field missing</t>
+  </si>
+  <si>
+    <t>1. Go to /register 
+2. Enter "WeakPassword123" as password 
+3. Click Register</t>
+  </si>
+  <si>
+    <t>Register with password under 8 characters</t>
+  </si>
+  <si>
+    <t>1. Go to /register 
+2. Enter "Short1!" as password 
+3. Fill rest of fields</t>
+  </si>
+  <si>
+    <t>Validation error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fail </t>
+  </si>
+  <si>
+    <t>Not As Expected</t>
   </si>
 </sst>
 </file>
@@ -1007,7 +1058,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1017,6 +1068,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1149,7 +1206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1190,12 +1247,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1208,20 +1259,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1232,6 +1276,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1399,13 +1462,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12.69921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="54.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.19921875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.796875" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.8984375" bestFit="1" customWidth="1"/>
@@ -1453,7 +1516,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>12</v>
@@ -1482,7 +1545,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>19</v>
@@ -1511,10 +1574,10 @@
         <v>21</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>22</v>
+        <v>264</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>13</v>
@@ -1531,19 +1594,19 @@
     </row>
     <row r="5" spans="1:9" ht="56.4" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>25</v>
+        <v>265</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>13</v>
@@ -1560,19 +1623,19 @@
     </row>
     <row r="6" spans="1:9" ht="52.8" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>28</v>
+        <v>266</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>13</v>
@@ -1587,79 +1650,79 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="55.2" customHeight="1">
+    <row r="7" spans="1:9" ht="64.2" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="E7" s="9" t="s">
+    </row>
+    <row r="8" spans="1:9" s="27" customFormat="1" ht="50.4" customHeight="1">
+      <c r="A8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="9" t="s">
+      <c r="B8" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="D8" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="E8" s="25" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="50.4" customHeight="1">
-      <c r="A8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>33</v>
+      <c r="F8" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="26" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="67.2" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>13</v>
@@ -1668,27 +1731,27 @@
         <v>14</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="63" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>43</v>
+        <v>267</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>13</v>
@@ -1697,27 +1760,27 @@
         <v>14</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="52.8" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>13</v>
@@ -1726,10 +1789,39 @@
         <v>14</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="41.4">
+      <c r="A12" t="s">
+        <v>280</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>288</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>287</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="30" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1782,19 +1874,19 @@
     </row>
     <row r="2" spans="1:9" ht="68.400000000000006" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>13</v>
@@ -1811,19 +1903,19 @@
     </row>
     <row r="3" spans="1:9" ht="64.2" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>52</v>
-      </c>
       <c r="D3" s="9" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>53</v>
+        <v>268</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>13</v>
@@ -1840,19 +1932,19 @@
     </row>
     <row r="4" spans="1:9" ht="63.6" customHeight="1">
       <c r="A4" s="8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>56</v>
+        <v>269</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>13</v>
@@ -1869,19 +1961,19 @@
     </row>
     <row r="5" spans="1:9" ht="64.8" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>59</v>
+        <v>270</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>13</v>
@@ -1898,19 +1990,19 @@
     </row>
     <row r="6" spans="1:9" ht="55.2">
       <c r="A6" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>13</v>
@@ -1927,19 +2019,19 @@
     </row>
     <row r="7" spans="1:9" ht="51" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>65</v>
+        <v>271</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>13</v>
@@ -1956,19 +2048,19 @@
     </row>
     <row r="8" spans="1:9" ht="76.2" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>13</v>
@@ -1977,27 +2069,27 @@
         <v>14</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="36" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>13</v>
@@ -2006,27 +2098,27 @@
         <v>14</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="64.2" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>13</v>
@@ -2035,27 +2127,27 @@
         <v>14</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="38.4" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>13</v>
@@ -2070,33 +2162,33 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="55.2">
-      <c r="A12" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>250</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="22" t="s">
-        <v>33</v>
+    <row r="12" spans="1:9" s="27" customFormat="1" ht="55.2">
+      <c r="A12" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="26" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2149,19 +2241,19 @@
     </row>
     <row r="2" spans="1:9" ht="51" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>13</v>
@@ -2178,19 +2270,19 @@
     </row>
     <row r="3" spans="1:9" ht="54" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>13</v>
@@ -2207,19 +2299,19 @@
     </row>
     <row r="4" spans="1:9" ht="49.2" customHeight="1">
       <c r="A4" s="8" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>79</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>87</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>13</v>
@@ -2236,19 +2328,19 @@
     </row>
     <row r="5" spans="1:9" ht="48" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>13</v>
@@ -2263,50 +2355,50 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="49.2" customHeight="1">
-      <c r="A6" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6" s="9" t="s">
+    <row r="6" spans="1:9" s="27" customFormat="1" ht="49.2" customHeight="1">
+      <c r="A6" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="E6" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" s="9" t="s">
+      <c r="F6" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="10" t="s">
-        <v>95</v>
+      <c r="I6" s="26" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="48.6" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>13</v>
@@ -2315,27 +2407,27 @@
         <v>14</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="48.6" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>13</v>
@@ -2344,27 +2436,27 @@
         <v>14</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="60.6" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>13</v>
@@ -2373,10 +2465,10 @@
         <v>14</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2429,19 +2521,19 @@
     </row>
     <row r="2" spans="1:9" ht="51" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>13</v>
@@ -2458,48 +2550,48 @@
     </row>
     <row r="3" spans="1:9" ht="50.4" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>13</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="48.6" customHeight="1">
       <c r="A4" s="8" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>13</v>
@@ -2516,19 +2608,19 @@
     </row>
     <row r="5" spans="1:9" ht="33" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>13</v>
@@ -2537,56 +2629,56 @@
         <v>14</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="50.4" customHeight="1">
-      <c r="A6" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="27" customFormat="1" ht="50.4" customHeight="1">
+      <c r="A6" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="26" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="48.6" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>13</v>
@@ -2595,10 +2687,10 @@
         <v>14</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2651,19 +2743,19 @@
     </row>
     <row r="2" spans="1:9" ht="34.200000000000003" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>13</v>
@@ -2680,19 +2772,19 @@
     </row>
     <row r="3" spans="1:9" ht="52.2" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>13</v>
@@ -2707,50 +2799,50 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.4" customHeight="1">
-      <c r="A4" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H4" s="9" t="s">
+    <row r="4" spans="1:9" s="27" customFormat="1" ht="50.4" customHeight="1">
+      <c r="A4" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="26" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="32.4" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>13</v>
@@ -2767,19 +2859,19 @@
     </row>
     <row r="6" spans="1:9" ht="51" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>13</v>
@@ -2796,19 +2888,19 @@
     </row>
     <row r="7" spans="1:9" ht="61.2" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>13</v>
@@ -2817,27 +2909,27 @@
         <v>14</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="36" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>13</v>
@@ -2854,19 +2946,19 @@
     </row>
     <row r="9" spans="1:9" ht="48" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>13</v>
@@ -2875,56 +2967,56 @@
         <v>14</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="49.2" customHeight="1">
-      <c r="A10" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H10" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="27" customFormat="1" ht="49.2" customHeight="1">
+      <c r="A10" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="26" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="38.4" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>13</v>
@@ -2989,19 +3081,19 @@
     </row>
     <row r="2" spans="1:9" ht="93" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>13</v>
@@ -3016,50 +3108,50 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="49.8" customHeight="1">
-      <c r="A3" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H3" s="9" t="s">
+    <row r="3" spans="1:9" s="27" customFormat="1" ht="49.8" customHeight="1">
+      <c r="A3" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="26" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="51" customHeight="1">
       <c r="A4" s="8" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>13</v>
@@ -3076,19 +3168,19 @@
     </row>
     <row r="5" spans="1:9" ht="66.599999999999994" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>13</v>
@@ -3097,56 +3189,56 @@
         <v>14</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="60.6" customHeight="1">
-      <c r="A6" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="27" customFormat="1" ht="60.6" customHeight="1">
+      <c r="A6" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="54" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>13</v>
@@ -3163,19 +3255,19 @@
     </row>
     <row r="8" spans="1:9" ht="46.8" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>13</v>
@@ -3192,31 +3284,31 @@
     </row>
     <row r="9" spans="1:9" ht="31.8" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>13</v>
+        <v>288</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3269,19 +3361,19 @@
     </row>
     <row r="2" spans="1:9" ht="60.6" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>13</v>
@@ -3290,27 +3382,27 @@
         <v>14</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="89.4" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>13</v>
@@ -3325,50 +3417,50 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="59.4" customHeight="1">
-      <c r="A4" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H4" s="9" t="s">
+    <row r="4" spans="1:9" s="27" customFormat="1" ht="59.4" customHeight="1">
+      <c r="A4" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="26" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="50.4" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>13</v>
@@ -3377,10 +3469,10 @@
         <v>14</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3390,14 +3482,14 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49DA1B9F-BD94-4BDE-82E4-461C86B23AB2}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="38.796875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.8984375" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.09765625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="38.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.09765625" style="22" customWidth="1"/>
     <col min="6" max="6" width="11.8984375" customWidth="1"/>
     <col min="7" max="9" width="10" customWidth="1"/>
     <col min="11" max="11" width="8.796875" customWidth="1"/>
@@ -3405,37 +3497,37 @@
   <sheetData>
     <row r="1" spans="1:9" ht="19.2" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>273</v>
-      </c>
-      <c r="D1" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="D1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="24"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="19"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E2" s="26"/>
+        <v>246</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="C2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E2" s="21"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -3443,16 +3535,16 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="5" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="B3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>156</v>
+        <v>255</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>147</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
@@ -3461,16 +3553,16 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>48</v>
+        <v>248</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>44</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
@@ -3479,18 +3571,18 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="5" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="B5" t="s">
-        <v>267</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>91</v>
+        <v>257</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="28"/>
+        <v>71</v>
+      </c>
+      <c r="E5" s="23"/>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
@@ -3498,65 +3590,132 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="5" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B6" t="s">
-        <v>268</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>109</v>
+        <v>258</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="5" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>181</v>
+        <v>179</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B8" t="s">
+        <v>259</v>
+      </c>
+      <c r="C8" t="s">
+        <v>261</v>
+      </c>
+      <c r="D8" t="s">
         <v>262</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="D8" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="C9" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="B9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B10" t="s">
+        <v>277</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B11" t="s">
+        <v>278</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B13" t="s">
+        <v>281</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="5"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="5"/>
+      <c r="D13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B14" t="s">
+        <v>282</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
